--- a/data/asistencia/Bravos 2026.xlsx
+++ b/data/asistencia/Bravos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="38">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -25,10 +25,10 @@
     <t>ZONA</t>
   </si>
   <si>
-    <t>EN PROCESO DE VENTA</t>
-  </si>
-  <si>
-    <t>VENDIDOS CON PRECIO</t>
+    <t>AFORO</t>
+  </si>
+  <si>
+    <t>VENDIDOS</t>
   </si>
   <si>
     <t>PROMOS</t>
@@ -61,16 +61,13 @@
     <t>PAQUETES PRECIO $1</t>
   </si>
   <si>
-    <t>PROMOCIONES</t>
-  </si>
-  <si>
     <t>BLOQUEOS</t>
   </si>
   <si>
-    <t>AFORO</t>
-  </si>
-  <si>
-    <t>OCUPADOS</t>
+    <t>EN PROCESO</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
   <si>
     <t>DISPONIBLES</t>
@@ -85,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>28.86%</t>
+    <t>30.19%</t>
   </si>
   <si>
     <t>Butaca 3ra Base</t>
   </si>
   <si>
-    <t>47.94%</t>
+    <t>48.69%</t>
   </si>
   <si>
     <t>General 1ra Base</t>
@@ -115,19 +112,19 @@
     <t>VIP</t>
   </si>
   <si>
-    <t>66.30%</t>
+    <t>67.66%</t>
   </si>
   <si>
     <t>Zona Gas Noel Butaca Central</t>
   </si>
   <si>
-    <t>30.84%</t>
+    <t>31.29%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>20.71%</t>
+    <t>21.17%</t>
   </si>
 </sst>
 </file>
@@ -187,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -204,20 +201,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -558,11 +546,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
-    <col min="2" max="19" width="25" customWidth="1"/>
+    <col min="2" max="18" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -585,7 +573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -640,480 +628,453 @@
       <c r="R5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="S5" s="6" t="s">
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6">
+        <v>828</v>
+      </c>
+      <c r="C6" s="6">
+        <v>110</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="6">
+        <v>32</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="6">
+        <v>37</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="6">
+        <v>5</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="6">
         <v>23</v>
       </c>
-      <c r="C6" s="7">
-        <v>103</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="L6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" s="6">
+        <v>43</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P6" s="6">
+        <v>250</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>578</v>
+      </c>
+      <c r="R6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="7">
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="6">
+        <v>534</v>
+      </c>
+      <c r="C7" s="6">
+        <v>51</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="6">
+        <v>10</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="6">
+        <v>28</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="6">
+        <v>10</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" s="6">
+        <v>157</v>
+      </c>
+      <c r="O7" s="6">
+        <v>4</v>
+      </c>
+      <c r="P7" s="6">
+        <v>260</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>274</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="6">
+        <v>1213</v>
+      </c>
+      <c r="C8" s="6">
+        <v>4</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="6">
+        <v>5</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P8" s="6">
+        <v>9</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>1204</v>
+      </c>
+      <c r="R8" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1324</v>
+      </c>
+      <c r="C9" s="6">
+        <v>14</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="6">
+        <v>2</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="6">
+        <v>12</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P9" s="6">
+        <v>28</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>1296</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="6">
+        <v>27</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="6">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P10" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>26</v>
+      </c>
+      <c r="R10" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="7">
+      <c r="B11" s="6">
+        <v>368</v>
+      </c>
+      <c r="C11" s="6">
+        <v>41</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="6">
+        <v>42</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="6">
+        <v>29</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="6">
+        <v>57</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="6">
+        <v>2</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N11" s="6">
+        <v>78</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P11" s="6">
+        <v>249</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>119</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="6">
+        <v>1109</v>
+      </c>
+      <c r="C12" s="6">
+        <v>151</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="6">
+        <v>61</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="6">
+        <v>32</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="6">
+        <v>49</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="6">
+        <v>16</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N12" s="6">
+        <v>38</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P12" s="6">
+        <v>347</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>762</v>
+      </c>
+      <c r="R12" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="7">
+        <f>SUM(B6:B12)</f>
+      </c>
+      <c r="C13" s="7">
+        <f>SUM(C6:C12)</f>
+      </c>
+      <c r="D13" s="7">
+        <f>SUM(D6:D12)</f>
+      </c>
+      <c r="E13" s="7">
+        <f>SUM(E6:E12)</f>
+      </c>
+      <c r="F13" s="7">
+        <f>SUM(F6:F12)</f>
+      </c>
+      <c r="G13" s="7">
+        <f>SUM(G6:G12)</f>
+      </c>
+      <c r="H13" s="7">
+        <f>SUM(H6:H12)</f>
+      </c>
+      <c r="I13" s="7">
+        <f>SUM(I6:I12)</f>
+      </c>
+      <c r="J13" s="7">
+        <f>SUM(J6:J12)</f>
+      </c>
+      <c r="K13" s="7">
+        <f>SUM(K6:K12)</f>
+      </c>
+      <c r="L13" s="7">
+        <f>SUM(L6:L12)</f>
+      </c>
+      <c r="M13" s="7">
+        <f>SUM(M6:M12)</f>
+      </c>
+      <c r="N13" s="7">
+        <f>SUM(N6:N12)</f>
+      </c>
+      <c r="O13" s="7">
+        <f>SUM(O6:O12)</f>
+      </c>
+      <c r="P13" s="7">
+        <f>SUM(P6:P12)</f>
+      </c>
+      <c r="Q13" s="7">
+        <f>SUM(Q6:Q12)</f>
+      </c>
+      <c r="R13" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="7">
-        <v>5</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" s="7">
-        <v>19</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O6" s="7">
-        <v>43</v>
-      </c>
-      <c r="P6" s="7">
-        <v>828</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>239</v>
-      </c>
-      <c r="R6" s="7">
-        <v>589</v>
-      </c>
-      <c r="S6" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="7">
-        <v>4</v>
-      </c>
-      <c r="C7" s="7">
-        <v>49</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="7">
-        <v>10</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="7">
-        <v>28</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="7">
-        <v>8</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O7" s="7">
-        <v>157</v>
-      </c>
-      <c r="P7" s="7">
-        <v>534</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>256</v>
-      </c>
-      <c r="R7" s="7">
-        <v>278</v>
-      </c>
-      <c r="S7" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="7">
-        <v>4</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="7">
-        <v>5</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P8" s="7">
-        <v>1213</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>9</v>
-      </c>
-      <c r="R8" s="7">
-        <v>1204</v>
-      </c>
-      <c r="S8" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="7">
-        <v>14</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="7">
-        <v>2</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="7">
-        <v>12</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P9" s="7">
-        <v>1324</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>28</v>
-      </c>
-      <c r="R9" s="7">
-        <v>1296</v>
-      </c>
-      <c r="S9" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="7">
-        <v>1</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P10" s="7">
-        <v>27</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>1</v>
-      </c>
-      <c r="R10" s="7">
-        <v>26</v>
-      </c>
-      <c r="S10" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="7">
-        <v>36</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="7">
-        <v>42</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="7">
-        <v>29</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="7">
-        <v>57</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" s="7">
-        <v>2</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O11" s="7">
-        <v>78</v>
-      </c>
-      <c r="P11" s="7">
-        <v>368</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>244</v>
-      </c>
-      <c r="R11" s="7">
-        <v>124</v>
-      </c>
-      <c r="S11" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="7">
-        <v>146</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="7">
-        <v>61</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="7">
-        <v>32</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="7">
-        <v>49</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="7">
-        <v>16</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O12" s="7">
-        <v>38</v>
-      </c>
-      <c r="P12" s="7">
-        <v>1109</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>342</v>
-      </c>
-      <c r="R12" s="7">
-        <v>767</v>
-      </c>
-      <c r="S12" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="9">
-        <f>SUM(B6:B12)</f>
-      </c>
-      <c r="C13" s="9">
-        <f>SUM(C6:C12)</f>
-      </c>
-      <c r="D13" s="9">
-        <f>SUM(D6:D12)</f>
-      </c>
-      <c r="E13" s="9">
-        <f>SUM(E6:E12)</f>
-      </c>
-      <c r="F13" s="9">
-        <f>SUM(F6:F12)</f>
-      </c>
-      <c r="G13" s="9">
-        <f>SUM(G6:G12)</f>
-      </c>
-      <c r="H13" s="9">
-        <f>SUM(H6:H12)</f>
-      </c>
-      <c r="I13" s="9">
-        <f>SUM(I6:I12)</f>
-      </c>
-      <c r="J13" s="9">
-        <f>SUM(J6:J12)</f>
-      </c>
-      <c r="K13" s="9">
-        <f>SUM(K6:K12)</f>
-      </c>
-      <c r="L13" s="9">
-        <f>SUM(L6:L12)</f>
-      </c>
-      <c r="M13" s="9">
-        <f>SUM(M6:M12)</f>
-      </c>
-      <c r="N13" s="9">
-        <f>SUM(N6:N12)</f>
-      </c>
-      <c r="O13" s="9">
-        <f>SUM(O6:O12)</f>
-      </c>
-      <c r="P13" s="9">
-        <f>SUM(P6:P12)</f>
-      </c>
-      <c r="Q13" s="9">
-        <f>SUM(Q6:Q12)</f>
-      </c>
-      <c r="R13" s="9">
-        <f>SUM(R6:R12)</f>
-      </c>
-      <c r="S13" s="10" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Bravos 2026.xlsx
+++ b/data/asistencia/Bravos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="39">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -25,49 +25,52 @@
     <t>ZONA</t>
   </si>
   <si>
+    <t>EN PROCESO DE VENTA</t>
+  </si>
+  <si>
+    <t>VENDIDOS CON PRECIO</t>
+  </si>
+  <si>
+    <t>PROMOS</t>
+  </si>
+  <si>
+    <t>CORTESÍAS</t>
+  </si>
+  <si>
+    <t>PRECIO $1</t>
+  </si>
+  <si>
+    <t>ABONOS VENDIDOS</t>
+  </si>
+  <si>
+    <t>ABONOS PROMOS</t>
+  </si>
+  <si>
+    <t>ABONOS CORTESÍAS</t>
+  </si>
+  <si>
+    <t>ABONOS PRECIO $1</t>
+  </si>
+  <si>
+    <t>PAQUETES</t>
+  </si>
+  <si>
+    <t>PAQUETES CORTESIAS</t>
+  </si>
+  <si>
+    <t>PAQUETES PRECIO $1</t>
+  </si>
+  <si>
+    <t>PROMOCIONES</t>
+  </si>
+  <si>
+    <t>BLOQUEOS</t>
+  </si>
+  <si>
     <t>AFORO</t>
   </si>
   <si>
-    <t>VENDIDOS</t>
-  </si>
-  <si>
-    <t>PROMOS</t>
-  </si>
-  <si>
-    <t>CORTESÍAS</t>
-  </si>
-  <si>
-    <t>PRECIO $1</t>
-  </si>
-  <si>
-    <t>ABONOS VENDIDOS</t>
-  </si>
-  <si>
-    <t>ABONOS PROMOS</t>
-  </si>
-  <si>
-    <t>ABONOS CORTESÍAS</t>
-  </si>
-  <si>
-    <t>ABONOS PRECIO $1</t>
-  </si>
-  <si>
-    <t>PAQUETES</t>
-  </si>
-  <si>
-    <t>PAQUETES CORTESIAS</t>
-  </si>
-  <si>
-    <t>PAQUETES PRECIO $1</t>
-  </si>
-  <si>
-    <t>BLOQUEOS</t>
-  </si>
-  <si>
-    <t>EN PROCESO</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
+    <t>OCUPADOS</t>
   </si>
   <si>
     <t>DISPONIBLES</t>
@@ -88,7 +91,7 @@
     <t>Butaca 3ra Base</t>
   </si>
   <si>
-    <t>48.69%</t>
+    <t>50.56%</t>
   </si>
   <si>
     <t>General 1ra Base</t>
@@ -124,7 +127,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>21.17%</t>
+    <t>21.36%</t>
   </si>
 </sst>
 </file>
@@ -184,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -201,11 +204,20 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -546,11 +558,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
-    <col min="2" max="18" width="25" customWidth="1"/>
+    <col min="2" max="19" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -573,7 +585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -628,453 +640,480 @@
       <c r="R5" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S5" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="6">
+        <v>22</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="7">
+        <v>110</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="7">
+        <v>32</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="7">
+        <v>37</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="7">
+        <v>5</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="7">
+        <v>23</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="7">
+        <v>43</v>
+      </c>
+      <c r="P6" s="7">
         <v>828</v>
       </c>
-      <c r="C6" s="6">
-        <v>110</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="6">
+      <c r="Q6" s="7">
+        <v>250</v>
+      </c>
+      <c r="R6" s="7">
+        <v>578</v>
+      </c>
+      <c r="S6" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="7">
+        <v>14</v>
+      </c>
+      <c r="C7" s="7">
+        <v>51</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="7">
+        <v>10</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="7">
+        <v>28</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="7">
+        <v>10</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" s="7">
+        <v>157</v>
+      </c>
+      <c r="P7" s="7">
+        <v>534</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>270</v>
+      </c>
+      <c r="R7" s="7">
+        <v>264</v>
+      </c>
+      <c r="S7" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="7">
+        <v>4</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="7">
+        <v>5</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="P8" s="7">
+        <v>1213</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>9</v>
+      </c>
+      <c r="R8" s="7">
+        <v>1204</v>
+      </c>
+      <c r="S8" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="7">
+        <v>14</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="7">
+        <v>12</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="P9" s="7">
+        <v>1324</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>28</v>
+      </c>
+      <c r="R9" s="7">
+        <v>1296</v>
+      </c>
+      <c r="S9" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="7">
+        <v>1</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="P10" s="7">
+        <v>27</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>1</v>
+      </c>
+      <c r="R10" s="7">
+        <v>26</v>
+      </c>
+      <c r="S10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="6">
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="7">
+        <v>41</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="7">
+        <v>42</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="7">
+        <v>29</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="7">
+        <v>57</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="7">
+        <v>2</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O11" s="7">
+        <v>78</v>
+      </c>
+      <c r="P11" s="7">
+        <v>368</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>249</v>
+      </c>
+      <c r="R11" s="7">
+        <v>119</v>
+      </c>
+      <c r="S11" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="7">
+        <v>151</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="7">
+        <v>61</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="7">
+        <v>32</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="7">
+        <v>49</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12" s="7">
+        <v>16</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O12" s="7">
+        <v>38</v>
+      </c>
+      <c r="P12" s="7">
+        <v>1109</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>347</v>
+      </c>
+      <c r="R12" s="7">
+        <v>762</v>
+      </c>
+      <c r="S12" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="6">
-        <v>5</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="6">
-        <v>23</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N6" s="6">
-        <v>43</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P6" s="6">
-        <v>250</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>578</v>
-      </c>
-      <c r="R6" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="6">
-        <v>534</v>
-      </c>
-      <c r="C7" s="6">
-        <v>51</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="6">
-        <v>10</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="6">
-        <v>28</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" s="6">
-        <v>10</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N7" s="6">
-        <v>157</v>
-      </c>
-      <c r="O7" s="6">
-        <v>4</v>
-      </c>
-      <c r="P7" s="6">
-        <v>260</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>274</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="6">
-        <v>1213</v>
-      </c>
-      <c r="C8" s="6">
-        <v>4</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="6">
-        <v>5</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P8" s="6">
-        <v>9</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>1204</v>
-      </c>
-      <c r="R8" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="6">
-        <v>1324</v>
-      </c>
-      <c r="C9" s="6">
-        <v>14</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="6">
-        <v>2</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="6">
-        <v>12</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P9" s="6">
-        <v>28</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>1296</v>
-      </c>
-      <c r="R9" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="6">
-        <v>27</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="6">
-        <v>1</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P10" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>26</v>
-      </c>
-      <c r="R10" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="6">
-        <v>368</v>
-      </c>
-      <c r="C11" s="6">
-        <v>41</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="6">
-        <v>42</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="6">
-        <v>29</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="6">
-        <v>57</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K11" s="6">
-        <v>2</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N11" s="6">
-        <v>78</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P11" s="6">
-        <v>249</v>
-      </c>
-      <c r="Q11" s="6">
-        <v>119</v>
-      </c>
-      <c r="R11" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="6">
-        <v>1109</v>
-      </c>
-      <c r="C12" s="6">
-        <v>151</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="6">
-        <v>61</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="6">
-        <v>32</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="6">
-        <v>49</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K12" s="6">
-        <v>16</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N12" s="6">
+      <c r="B13" s="9">
+        <f>SUM(B6:B12)</f>
+      </c>
+      <c r="C13" s="9">
+        <f>SUM(C6:C12)</f>
+      </c>
+      <c r="D13" s="9">
+        <f>SUM(D6:D12)</f>
+      </c>
+      <c r="E13" s="9">
+        <f>SUM(E6:E12)</f>
+      </c>
+      <c r="F13" s="9">
+        <f>SUM(F6:F12)</f>
+      </c>
+      <c r="G13" s="9">
+        <f>SUM(G6:G12)</f>
+      </c>
+      <c r="H13" s="9">
+        <f>SUM(H6:H12)</f>
+      </c>
+      <c r="I13" s="9">
+        <f>SUM(I6:I12)</f>
+      </c>
+      <c r="J13" s="9">
+        <f>SUM(J6:J12)</f>
+      </c>
+      <c r="K13" s="9">
+        <f>SUM(K6:K12)</f>
+      </c>
+      <c r="L13" s="9">
+        <f>SUM(L6:L12)</f>
+      </c>
+      <c r="M13" s="9">
+        <f>SUM(M6:M12)</f>
+      </c>
+      <c r="N13" s="9">
+        <f>SUM(N6:N12)</f>
+      </c>
+      <c r="O13" s="9">
+        <f>SUM(O6:O12)</f>
+      </c>
+      <c r="P13" s="9">
+        <f>SUM(P6:P12)</f>
+      </c>
+      <c r="Q13" s="9">
+        <f>SUM(Q6:Q12)</f>
+      </c>
+      <c r="R13" s="9">
+        <f>SUM(R6:R12)</f>
+      </c>
+      <c r="S13" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P12" s="6">
-        <v>347</v>
-      </c>
-      <c r="Q12" s="6">
-        <v>762</v>
-      </c>
-      <c r="R12" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="7">
-        <f>SUM(B6:B12)</f>
-      </c>
-      <c r="C13" s="7">
-        <f>SUM(C6:C12)</f>
-      </c>
-      <c r="D13" s="7">
-        <f>SUM(D6:D12)</f>
-      </c>
-      <c r="E13" s="7">
-        <f>SUM(E6:E12)</f>
-      </c>
-      <c r="F13" s="7">
-        <f>SUM(F6:F12)</f>
-      </c>
-      <c r="G13" s="7">
-        <f>SUM(G6:G12)</f>
-      </c>
-      <c r="H13" s="7">
-        <f>SUM(H6:H12)</f>
-      </c>
-      <c r="I13" s="7">
-        <f>SUM(I6:I12)</f>
-      </c>
-      <c r="J13" s="7">
-        <f>SUM(J6:J12)</f>
-      </c>
-      <c r="K13" s="7">
-        <f>SUM(K6:K12)</f>
-      </c>
-      <c r="L13" s="7">
-        <f>SUM(L6:L12)</f>
-      </c>
-      <c r="M13" s="7">
-        <f>SUM(M6:M12)</f>
-      </c>
-      <c r="N13" s="7">
-        <f>SUM(N6:N12)</f>
-      </c>
-      <c r="O13" s="7">
-        <f>SUM(O6:O12)</f>
-      </c>
-      <c r="P13" s="7">
-        <f>SUM(P6:P12)</f>
-      </c>
-      <c r="Q13" s="7">
-        <f>SUM(Q6:Q12)</f>
-      </c>
-      <c r="R13" s="7" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Bravos 2026.xlsx
+++ b/data/asistencia/Bravos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="42">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -19,16 +19,16 @@
     <t/>
   </si>
   <si>
-    <t>Juego Inaugural: Guerreros vs Bravos</t>
+    <t>Juego Inaugural: Naranjeros vs Bravas</t>
   </si>
   <si>
     <t>ZONA</t>
   </si>
   <si>
-    <t>EN PROCESO DE VENTA</t>
-  </si>
-  <si>
-    <t>VENDIDOS CON PRECIO</t>
+    <t>AFORO</t>
+  </si>
+  <si>
+    <t>VENDIDOS</t>
   </si>
   <si>
     <t>PROMOS</t>
@@ -61,16 +61,13 @@
     <t>PAQUETES PRECIO $1</t>
   </si>
   <si>
-    <t>PROMOCIONES</t>
-  </si>
-  <si>
     <t>BLOQUEOS</t>
   </si>
   <si>
-    <t>AFORO</t>
-  </si>
-  <si>
-    <t>OCUPADOS</t>
+    <t>EN PROCESO</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
   <si>
     <t>DISPONIBLES</t>
@@ -85,49 +82,61 @@
     <t>-</t>
   </si>
   <si>
-    <t>30.19%</t>
+    <t>71.86%</t>
   </si>
   <si>
     <t>Butaca 3ra Base</t>
   </si>
   <si>
-    <t>50.56%</t>
+    <t>89.33%</t>
   </si>
   <si>
     <t>General 1ra Base</t>
   </si>
   <si>
-    <t>0.74%</t>
+    <t>7.25%</t>
   </si>
   <si>
     <t>General 3ra Base</t>
   </si>
   <si>
-    <t>2.11%</t>
+    <t>18.19%</t>
+  </si>
+  <si>
+    <t>Palcos</t>
+  </si>
+  <si>
+    <t>54.04%</t>
+  </si>
+  <si>
+    <t>Parrilladas</t>
+  </si>
+  <si>
+    <t>16.67%</t>
   </si>
   <si>
     <t>Personas con Discapacidad</t>
   </si>
   <si>
-    <t>3.70%</t>
+    <t>33.33%</t>
   </si>
   <si>
     <t>VIP</t>
   </si>
   <si>
-    <t>67.66%</t>
+    <t>98.37%</t>
   </si>
   <si>
     <t>Zona Gas Noel Butaca Central</t>
   </si>
   <si>
-    <t>31.29%</t>
+    <t>87.92%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>21.36%</t>
+    <t>46.49%</t>
   </si>
 </sst>
 </file>
@@ -187,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -204,20 +213,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -558,11 +558,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="41" customWidth="1"/>
-    <col min="2" max="19" width="25" customWidth="1"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="18" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -585,7 +585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -640,484 +640,569 @@
       <c r="R5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="S5" s="6" t="s">
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6">
+        <v>828</v>
+      </c>
+      <c r="C6" s="6">
+        <v>182</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="6">
+        <v>326</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="6">
+        <v>51</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="6">
+        <v>36</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P6" s="6">
+        <v>595</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>233</v>
+      </c>
+      <c r="R6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="7">
-        <v>110</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="7">
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="6">
+        <v>534</v>
+      </c>
+      <c r="C7" s="6">
+        <v>66</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="6">
+        <v>340</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="6">
+        <v>43</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="6">
+        <v>28</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P7" s="6">
+        <v>477</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>57</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="6">
+        <v>1213</v>
+      </c>
+      <c r="C8" s="6">
+        <v>9</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="6">
+        <v>71</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="6">
+        <v>8</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P8" s="6">
+        <v>88</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>1125</v>
+      </c>
+      <c r="R8" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="6">
+        <v>2018</v>
+      </c>
+      <c r="C9" s="6">
+        <v>37</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="6">
+        <v>322</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="6">
+        <v>6</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="6">
+        <v>2</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P9" s="6">
+        <v>367</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>1651</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="6">
+        <v>198</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="6">
+        <v>18</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="6">
+        <v>71</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" s="6">
+        <v>18</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P10" s="6">
+        <v>107</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>91</v>
+      </c>
+      <c r="R10" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="7">
+      <c r="B11" s="6">
+        <v>180</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N11" s="6">
+        <v>30</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P11" s="6">
+        <v>30</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>150</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="6">
+        <v>27</v>
+      </c>
+      <c r="C12" s="6">
+        <v>3</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="6">
+        <v>5</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="6">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P12" s="6">
+        <v>9</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>18</v>
+      </c>
+      <c r="R12" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="6">
+        <v>368</v>
+      </c>
+      <c r="C13" s="6">
+        <v>16</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="6">
+        <v>215</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="6">
+        <v>43</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="6">
+        <v>40</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="6">
+        <v>1</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N13" s="6">
+        <v>47</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P13" s="6">
+        <v>362</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>6</v>
+      </c>
+      <c r="R13" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="7">
-        <v>5</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" s="7">
-        <v>23</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O6" s="7">
-        <v>43</v>
-      </c>
-      <c r="P6" s="7">
-        <v>828</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>250</v>
-      </c>
-      <c r="R6" s="7">
-        <v>578</v>
-      </c>
-      <c r="S6" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="6">
+        <v>1109</v>
+      </c>
+      <c r="C14" s="6">
+        <v>218</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="6">
+        <v>514</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="6">
+        <v>133</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="6">
+        <v>48</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="6">
         <v>25</v>
       </c>
-      <c r="B7" s="7">
-        <v>14</v>
-      </c>
-      <c r="C7" s="7">
-        <v>51</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="7">
-        <v>10</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="7">
-        <v>28</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="7">
-        <v>10</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O7" s="7">
-        <v>157</v>
-      </c>
-      <c r="P7" s="7">
-        <v>534</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>270</v>
-      </c>
-      <c r="R7" s="7">
-        <v>264</v>
-      </c>
-      <c r="S7" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="7">
-        <v>4</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="7">
-        <v>5</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P8" s="7">
-        <v>1213</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>9</v>
-      </c>
-      <c r="R8" s="7">
-        <v>1204</v>
-      </c>
-      <c r="S8" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="7">
-        <v>14</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="7">
-        <v>2</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="7">
-        <v>12</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P9" s="7">
-        <v>1324</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>28</v>
-      </c>
-      <c r="R9" s="7">
-        <v>1296</v>
-      </c>
-      <c r="S9" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="7">
-        <v>1</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P10" s="7">
-        <v>27</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>1</v>
-      </c>
-      <c r="R10" s="7">
-        <v>26</v>
-      </c>
-      <c r="S10" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="7">
+      <c r="L14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" s="6">
+        <v>37</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P14" s="6">
+        <v>975</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>134</v>
+      </c>
+      <c r="R14" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="7">
+        <f>SUM(B6:B14)</f>
+      </c>
+      <c r="C15" s="7">
+        <f>SUM(C6:C14)</f>
+      </c>
+      <c r="D15" s="7">
+        <f>SUM(D6:D14)</f>
+      </c>
+      <c r="E15" s="7">
+        <f>SUM(E6:E14)</f>
+      </c>
+      <c r="F15" s="7">
+        <f>SUM(F6:F14)</f>
+      </c>
+      <c r="G15" s="7">
+        <f>SUM(G6:G14)</f>
+      </c>
+      <c r="H15" s="7">
+        <f>SUM(H6:H14)</f>
+      </c>
+      <c r="I15" s="7">
+        <f>SUM(I6:I14)</f>
+      </c>
+      <c r="J15" s="7">
+        <f>SUM(J6:J14)</f>
+      </c>
+      <c r="K15" s="7">
+        <f>SUM(K6:K14)</f>
+      </c>
+      <c r="L15" s="7">
+        <f>SUM(L6:L14)</f>
+      </c>
+      <c r="M15" s="7">
+        <f>SUM(M6:M14)</f>
+      </c>
+      <c r="N15" s="7">
+        <f>SUM(N6:N14)</f>
+      </c>
+      <c r="O15" s="7">
+        <f>SUM(O6:O14)</f>
+      </c>
+      <c r="P15" s="7">
+        <f>SUM(P6:P14)</f>
+      </c>
+      <c r="Q15" s="7">
+        <f>SUM(Q6:Q14)</f>
+      </c>
+      <c r="R15" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="7">
-        <v>42</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="7">
-        <v>29</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="7">
-        <v>57</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" s="7">
-        <v>2</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O11" s="7">
-        <v>78</v>
-      </c>
-      <c r="P11" s="7">
-        <v>368</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>249</v>
-      </c>
-      <c r="R11" s="7">
-        <v>119</v>
-      </c>
-      <c r="S11" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="7">
-        <v>151</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="7">
-        <v>61</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="7">
-        <v>32</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="7">
-        <v>49</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="7">
-        <v>16</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O12" s="7">
-        <v>38</v>
-      </c>
-      <c r="P12" s="7">
-        <v>1109</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>347</v>
-      </c>
-      <c r="R12" s="7">
-        <v>762</v>
-      </c>
-      <c r="S12" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="9">
-        <f>SUM(B6:B12)</f>
-      </c>
-      <c r="C13" s="9">
-        <f>SUM(C6:C12)</f>
-      </c>
-      <c r="D13" s="9">
-        <f>SUM(D6:D12)</f>
-      </c>
-      <c r="E13" s="9">
-        <f>SUM(E6:E12)</f>
-      </c>
-      <c r="F13" s="9">
-        <f>SUM(F6:F12)</f>
-      </c>
-      <c r="G13" s="9">
-        <f>SUM(G6:G12)</f>
-      </c>
-      <c r="H13" s="9">
-        <f>SUM(H6:H12)</f>
-      </c>
-      <c r="I13" s="9">
-        <f>SUM(I6:I12)</f>
-      </c>
-      <c r="J13" s="9">
-        <f>SUM(J6:J12)</f>
-      </c>
-      <c r="K13" s="9">
-        <f>SUM(K6:K12)</f>
-      </c>
-      <c r="L13" s="9">
-        <f>SUM(L6:L12)</f>
-      </c>
-      <c r="M13" s="9">
-        <f>SUM(M6:M12)</f>
-      </c>
-      <c r="N13" s="9">
-        <f>SUM(N6:N12)</f>
-      </c>
-      <c r="O13" s="9">
-        <f>SUM(O6:O12)</f>
-      </c>
-      <c r="P13" s="9">
-        <f>SUM(P6:P12)</f>
-      </c>
-      <c r="Q13" s="9">
-        <f>SUM(Q6:Q12)</f>
-      </c>
-      <c r="R13" s="9">
-        <f>SUM(R6:R12)</f>
-      </c>
-      <c r="S13" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/asistencia/Bravos 2026.xlsx
+++ b/data/asistencia/Bravos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="38">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -25,10 +25,10 @@
     <t>ZONA</t>
   </si>
   <si>
-    <t>EN PROCESO DE VENTA</t>
-  </si>
-  <si>
-    <t>VENDIDOS CON PRECIO</t>
+    <t>AFORO</t>
+  </si>
+  <si>
+    <t>VENDIDOS</t>
   </si>
   <si>
     <t>PROMOS</t>
@@ -61,16 +61,13 @@
     <t>PAQUETES PRECIO $1</t>
   </si>
   <si>
-    <t>PROMOCIONES</t>
-  </si>
-  <si>
     <t>BLOQUEOS</t>
   </si>
   <si>
-    <t>AFORO</t>
-  </si>
-  <si>
-    <t>OCUPADOS</t>
+    <t>EN PROCESO</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
   <si>
     <t>DISPONIBLES</t>
@@ -85,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>33.94%</t>
+    <t>35.02%</t>
   </si>
   <si>
     <t>Butaca 3ra Base</t>
   </si>
   <si>
-    <t>54.68%</t>
+    <t>55.06%</t>
   </si>
   <si>
     <t>General 1ra Base</t>
@@ -103,7 +100,7 @@
     <t>General 3ra Base</t>
   </si>
   <si>
-    <t>2.11%</t>
+    <t>2.19%</t>
   </si>
   <si>
     <t>Personas con Discapacidad</t>
@@ -115,19 +112,19 @@
     <t>VIP</t>
   </si>
   <si>
-    <t>72.01%</t>
+    <t>75.82%</t>
   </si>
   <si>
     <t>Zona Gas Noel Butaca Central</t>
   </si>
   <si>
-    <t>36.97%</t>
+    <t>39.13%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>23.80%</t>
+    <t>24.73%</t>
   </si>
 </sst>
 </file>
@@ -187,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -204,20 +201,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -558,11 +546,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
-    <col min="2" max="19" width="25" customWidth="1"/>
+    <col min="2" max="18" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -585,7 +573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -640,480 +628,453 @@
       <c r="R5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="S5" s="6" t="s">
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6">
+        <v>828</v>
+      </c>
+      <c r="C6" s="6">
+        <v>150</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="6">
+        <v>32</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="6">
+        <v>37</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="6">
+        <v>5</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="6">
         <v>23</v>
       </c>
-      <c r="C6" s="7">
-        <v>141</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="L6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" s="6">
+        <v>43</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P6" s="6">
+        <v>290</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>538</v>
+      </c>
+      <c r="R6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="7">
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="6">
+        <v>534</v>
+      </c>
+      <c r="C7" s="6">
+        <v>81</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="6">
+        <v>10</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="6">
+        <v>28</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="6">
+        <v>11</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" s="6">
+        <v>157</v>
+      </c>
+      <c r="O7" s="6">
+        <v>7</v>
+      </c>
+      <c r="P7" s="6">
+        <v>294</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>240</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="6">
+        <v>1213</v>
+      </c>
+      <c r="C8" s="6">
+        <v>4</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="6">
+        <v>5</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P8" s="6">
+        <v>9</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>1204</v>
+      </c>
+      <c r="R8" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1324</v>
+      </c>
+      <c r="C9" s="6">
+        <v>15</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="6">
+        <v>2</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="6">
+        <v>12</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P9" s="6">
+        <v>29</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>1295</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="6">
+        <v>27</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="6">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P10" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>26</v>
+      </c>
+      <c r="R10" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="7">
+      <c r="B11" s="6">
+        <v>368</v>
+      </c>
+      <c r="C11" s="6">
+        <v>63</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="6">
+        <v>50</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="6">
+        <v>29</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="6">
+        <v>57</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="6">
+        <v>2</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N11" s="6">
+        <v>78</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P11" s="6">
+        <v>279</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>89</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="6">
+        <v>1109</v>
+      </c>
+      <c r="C12" s="6">
+        <v>224</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="6">
+        <v>65</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="6">
+        <v>32</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="6">
+        <v>49</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="6">
+        <v>26</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N12" s="6">
+        <v>38</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P12" s="6">
+        <v>434</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>675</v>
+      </c>
+      <c r="R12" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="7">
+        <f>SUM(B6:B12)</f>
+      </c>
+      <c r="C13" s="7">
+        <f>SUM(C6:C12)</f>
+      </c>
+      <c r="D13" s="7">
+        <f>SUM(D6:D12)</f>
+      </c>
+      <c r="E13" s="7">
+        <f>SUM(E6:E12)</f>
+      </c>
+      <c r="F13" s="7">
+        <f>SUM(F6:F12)</f>
+      </c>
+      <c r="G13" s="7">
+        <f>SUM(G6:G12)</f>
+      </c>
+      <c r="H13" s="7">
+        <f>SUM(H6:H12)</f>
+      </c>
+      <c r="I13" s="7">
+        <f>SUM(I6:I12)</f>
+      </c>
+      <c r="J13" s="7">
+        <f>SUM(J6:J12)</f>
+      </c>
+      <c r="K13" s="7">
+        <f>SUM(K6:K12)</f>
+      </c>
+      <c r="L13" s="7">
+        <f>SUM(L6:L12)</f>
+      </c>
+      <c r="M13" s="7">
+        <f>SUM(M6:M12)</f>
+      </c>
+      <c r="N13" s="7">
+        <f>SUM(N6:N12)</f>
+      </c>
+      <c r="O13" s="7">
+        <f>SUM(O6:O12)</f>
+      </c>
+      <c r="P13" s="7">
+        <f>SUM(P6:P12)</f>
+      </c>
+      <c r="Q13" s="7">
+        <f>SUM(Q6:Q12)</f>
+      </c>
+      <c r="R13" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="7">
-        <v>5</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" s="7">
-        <v>23</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O6" s="7">
-        <v>43</v>
-      </c>
-      <c r="P6" s="7">
-        <v>828</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>281</v>
-      </c>
-      <c r="R6" s="7">
-        <v>547</v>
-      </c>
-      <c r="S6" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="7">
-        <v>5</v>
-      </c>
-      <c r="C7" s="7">
-        <v>81</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="7">
-        <v>10</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="7">
-        <v>28</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="7">
-        <v>11</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O7" s="7">
-        <v>157</v>
-      </c>
-      <c r="P7" s="7">
-        <v>534</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>292</v>
-      </c>
-      <c r="R7" s="7">
-        <v>242</v>
-      </c>
-      <c r="S7" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="7">
-        <v>4</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="7">
-        <v>5</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P8" s="7">
-        <v>1213</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>9</v>
-      </c>
-      <c r="R8" s="7">
-        <v>1204</v>
-      </c>
-      <c r="S8" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="7">
-        <v>14</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="7">
-        <v>2</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="7">
-        <v>12</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P9" s="7">
-        <v>1324</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>28</v>
-      </c>
-      <c r="R9" s="7">
-        <v>1296</v>
-      </c>
-      <c r="S9" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="7">
-        <v>1</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P10" s="7">
-        <v>27</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>1</v>
-      </c>
-      <c r="R10" s="7">
-        <v>26</v>
-      </c>
-      <c r="S10" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="7">
-        <v>57</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="7">
-        <v>42</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="7">
-        <v>29</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="7">
-        <v>57</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" s="7">
-        <v>2</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O11" s="7">
-        <v>78</v>
-      </c>
-      <c r="P11" s="7">
-        <v>368</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>265</v>
-      </c>
-      <c r="R11" s="7">
-        <v>103</v>
-      </c>
-      <c r="S11" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="7">
-        <v>2</v>
-      </c>
-      <c r="C12" s="7">
-        <v>198</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="7">
-        <v>65</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="7">
-        <v>32</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="7">
-        <v>49</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="7">
-        <v>26</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O12" s="7">
-        <v>38</v>
-      </c>
-      <c r="P12" s="7">
-        <v>1109</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>410</v>
-      </c>
-      <c r="R12" s="7">
-        <v>699</v>
-      </c>
-      <c r="S12" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="9">
-        <f>SUM(B6:B12)</f>
-      </c>
-      <c r="C13" s="9">
-        <f>SUM(C6:C12)</f>
-      </c>
-      <c r="D13" s="9">
-        <f>SUM(D6:D12)</f>
-      </c>
-      <c r="E13" s="9">
-        <f>SUM(E6:E12)</f>
-      </c>
-      <c r="F13" s="9">
-        <f>SUM(F6:F12)</f>
-      </c>
-      <c r="G13" s="9">
-        <f>SUM(G6:G12)</f>
-      </c>
-      <c r="H13" s="9">
-        <f>SUM(H6:H12)</f>
-      </c>
-      <c r="I13" s="9">
-        <f>SUM(I6:I12)</f>
-      </c>
-      <c r="J13" s="9">
-        <f>SUM(J6:J12)</f>
-      </c>
-      <c r="K13" s="9">
-        <f>SUM(K6:K12)</f>
-      </c>
-      <c r="L13" s="9">
-        <f>SUM(L6:L12)</f>
-      </c>
-      <c r="M13" s="9">
-        <f>SUM(M6:M12)</f>
-      </c>
-      <c r="N13" s="9">
-        <f>SUM(N6:N12)</f>
-      </c>
-      <c r="O13" s="9">
-        <f>SUM(O6:O12)</f>
-      </c>
-      <c r="P13" s="9">
-        <f>SUM(P6:P12)</f>
-      </c>
-      <c r="Q13" s="9">
-        <f>SUM(Q6:Q12)</f>
-      </c>
-      <c r="R13" s="9">
-        <f>SUM(R6:R12)</f>
-      </c>
-      <c r="S13" s="10" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Bravos 2026.xlsx
+++ b/data/asistencia/Bravos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="40">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>35.02%</t>
+    <t>36.35%</t>
   </si>
   <si>
     <t>Butaca 3ra Base</t>
   </si>
   <si>
-    <t>55.06%</t>
+    <t>57.30%</t>
   </si>
   <si>
     <t>General 1ra Base</t>
@@ -103,6 +103,12 @@
     <t>2.19%</t>
   </si>
   <si>
+    <t>Parrilladas</t>
+  </si>
+  <si>
+    <t>0.00%</t>
+  </si>
+  <si>
     <t>Personas con Discapacidad</t>
   </si>
   <si>
@@ -112,19 +118,19 @@
     <t>VIP</t>
   </si>
   <si>
-    <t>75.82%</t>
+    <t>77.72%</t>
   </si>
   <si>
     <t>Zona Gas Noel Butaca Central</t>
   </si>
   <si>
-    <t>39.13%</t>
+    <t>41.21%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>24.73%</t>
+    <t>24.88%</t>
   </si>
 </sst>
 </file>
@@ -546,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
@@ -637,7 +643,7 @@
         <v>828</v>
       </c>
       <c r="C6" s="6">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -676,10 +682,10 @@
         <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="Q6" s="6">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -693,7 +699,7 @@
         <v>534</v>
       </c>
       <c r="C7" s="6">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -732,10 +738,10 @@
         <v>7</v>
       </c>
       <c r="P7" s="6">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="Q7" s="6">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -858,7 +864,7 @@
         <v>30</v>
       </c>
       <c r="B10" s="6">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>22</v>
@@ -872,8 +878,8 @@
       <c r="F10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="6">
-        <v>1</v>
+      <c r="G10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>22</v>
@@ -899,11 +905,11 @@
       <c r="O10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P10" s="6">
-        <v>1</v>
+      <c r="P10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="Q10" s="6">
-        <v>26</v>
+        <v>180</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -914,34 +920,34 @@
         <v>32</v>
       </c>
       <c r="B11" s="6">
-        <v>368</v>
-      </c>
-      <c r="C11" s="6">
-        <v>63</v>
+        <v>27</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="6">
-        <v>50</v>
+      <c r="E11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G11" s="6">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="6">
-        <v>57</v>
+      <c r="I11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="6">
-        <v>2</v>
+      <c r="K11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>22</v>
@@ -949,17 +955,17 @@
       <c r="M11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N11" s="6">
-        <v>78</v>
+      <c r="N11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>279</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="6">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
@@ -970,34 +976,34 @@
         <v>34</v>
       </c>
       <c r="B12" s="6">
-        <v>1109</v>
+        <v>368</v>
       </c>
       <c r="C12" s="6">
-        <v>224</v>
+        <v>65</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G12" s="6">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="6">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="K12" s="6">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>22</v>
@@ -1006,79 +1012,135 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>434</v>
+        <v>286</v>
       </c>
       <c r="Q12" s="6">
-        <v>675</v>
+        <v>82</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="7">
-        <f>SUM(B6:B12)</f>
-      </c>
-      <c r="C13" s="7">
-        <f>SUM(C6:C12)</f>
-      </c>
-      <c r="D13" s="7">
-        <f>SUM(D6:D12)</f>
-      </c>
-      <c r="E13" s="7">
-        <f>SUM(E6:E12)</f>
-      </c>
-      <c r="F13" s="7">
-        <f>SUM(F6:F12)</f>
-      </c>
-      <c r="G13" s="7">
-        <f>SUM(G6:G12)</f>
-      </c>
-      <c r="H13" s="7">
-        <f>SUM(H6:H12)</f>
-      </c>
-      <c r="I13" s="7">
-        <f>SUM(I6:I12)</f>
-      </c>
-      <c r="J13" s="7">
-        <f>SUM(J6:J12)</f>
-      </c>
-      <c r="K13" s="7">
-        <f>SUM(K6:K12)</f>
-      </c>
-      <c r="L13" s="7">
-        <f>SUM(L6:L12)</f>
-      </c>
-      <c r="M13" s="7">
-        <f>SUM(M6:M12)</f>
-      </c>
-      <c r="N13" s="7">
-        <f>SUM(N6:N12)</f>
-      </c>
-      <c r="O13" s="7">
-        <f>SUM(O6:O12)</f>
-      </c>
-      <c r="P13" s="7">
-        <f>SUM(P6:P12)</f>
-      </c>
-      <c r="Q13" s="7">
-        <f>SUM(Q6:Q12)</f>
-      </c>
-      <c r="R13" s="7" t="s">
+      <c r="B13" s="6">
+        <v>1109</v>
+      </c>
+      <c r="C13" s="6">
+        <v>241</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="6">
+        <v>65</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="6">
+        <v>32</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="6">
+        <v>49</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="6">
+        <v>26</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N13" s="6">
+        <v>44</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P13" s="6">
+        <v>457</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>652</v>
+      </c>
+      <c r="R13" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="7">
+        <f>SUM(B6:B13)</f>
+      </c>
+      <c r="C14" s="7">
+        <f>SUM(C6:C13)</f>
+      </c>
+      <c r="D14" s="7">
+        <f>SUM(D6:D13)</f>
+      </c>
+      <c r="E14" s="7">
+        <f>SUM(E6:E13)</f>
+      </c>
+      <c r="F14" s="7">
+        <f>SUM(F6:F13)</f>
+      </c>
+      <c r="G14" s="7">
+        <f>SUM(G6:G13)</f>
+      </c>
+      <c r="H14" s="7">
+        <f>SUM(H6:H13)</f>
+      </c>
+      <c r="I14" s="7">
+        <f>SUM(I6:I13)</f>
+      </c>
+      <c r="J14" s="7">
+        <f>SUM(J6:J13)</f>
+      </c>
+      <c r="K14" s="7">
+        <f>SUM(K6:K13)</f>
+      </c>
+      <c r="L14" s="7">
+        <f>SUM(L6:L13)</f>
+      </c>
+      <c r="M14" s="7">
+        <f>SUM(M6:M13)</f>
+      </c>
+      <c r="N14" s="7">
+        <f>SUM(N6:N13)</f>
+      </c>
+      <c r="O14" s="7">
+        <f>SUM(O6:O13)</f>
+      </c>
+      <c r="P14" s="7">
+        <f>SUM(P6:P13)</f>
+      </c>
+      <c r="Q14" s="7">
+        <f>SUM(Q6:Q13)</f>
+      </c>
+      <c r="R14" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/asistencia/Bravos 2026.xlsx
+++ b/data/asistencia/Bravos 2026.xlsx
@@ -82,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>36.35%</t>
+    <t>39.73%</t>
   </si>
   <si>
     <t>Butaca 3ra Base</t>
   </si>
   <si>
-    <t>57.30%</t>
+    <t>57.87%</t>
   </si>
   <si>
     <t>General 1ra Base</t>
@@ -118,19 +118,19 @@
     <t>VIP</t>
   </si>
   <si>
-    <t>77.72%</t>
+    <t>78.80%</t>
   </si>
   <si>
     <t>Zona Gas Noel Butaca Central</t>
   </si>
   <si>
-    <t>41.21%</t>
+    <t>43.10%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>24.88%</t>
+    <t>25.88%</t>
   </si>
 </sst>
 </file>
@@ -643,7 +643,7 @@
         <v>828</v>
       </c>
       <c r="C6" s="6">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -682,10 +682,10 @@
         <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>301</v>
+        <v>329</v>
       </c>
       <c r="Q6" s="6">
-        <v>527</v>
+        <v>499</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -699,7 +699,7 @@
         <v>534</v>
       </c>
       <c r="C7" s="6">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -723,7 +723,7 @@
         <v>22</v>
       </c>
       <c r="K7" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>22</v>
@@ -738,10 +738,10 @@
         <v>7</v>
       </c>
       <c r="P7" s="6">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q7" s="6">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -1012,16 +1012,16 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q12" s="6">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>35</v>
@@ -1035,7 +1035,7 @@
         <v>1109</v>
       </c>
       <c r="C13" s="6">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1059,7 +1059,7 @@
         <v>22</v>
       </c>
       <c r="K13" s="6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>22</v>
@@ -1068,16 +1068,16 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="Q13" s="6">
-        <v>652</v>
+        <v>631</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>

--- a/data/asistencia/Bravos 2026.xlsx
+++ b/data/asistencia/Bravos 2026.xlsx
@@ -82,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>39.73%</t>
+    <t>41.06%</t>
   </si>
   <si>
     <t>Butaca 3ra Base</t>
   </si>
   <si>
-    <t>57.87%</t>
+    <t>58.24%</t>
   </si>
   <si>
     <t>General 1ra Base</t>
@@ -124,13 +124,13 @@
     <t>Zona Gas Noel Butaca Central</t>
   </si>
   <si>
-    <t>43.10%</t>
+    <t>44.18%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>25.88%</t>
+    <t>26.33%</t>
   </si>
 </sst>
 </file>
@@ -643,7 +643,7 @@
         <v>828</v>
       </c>
       <c r="C6" s="6">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -682,10 +682,10 @@
         <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="Q6" s="6">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -699,7 +699,7 @@
         <v>534</v>
       </c>
       <c r="C7" s="6">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -738,10 +738,10 @@
         <v>7</v>
       </c>
       <c r="P7" s="6">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q7" s="6">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -1035,7 +1035,7 @@
         <v>1109</v>
       </c>
       <c r="C13" s="6">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1074,10 +1074,10 @@
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="Q13" s="6">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>

--- a/data/asistencia/Bravos 2026.xlsx
+++ b/data/asistencia/Bravos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="40">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,25 +82,25 @@
     <t>-</t>
   </si>
   <si>
-    <t>41.06%</t>
+    <t>46.01%</t>
   </si>
   <si>
     <t>Butaca 3ra Base</t>
   </si>
   <si>
-    <t>58.24%</t>
+    <t>49.44%</t>
   </si>
   <si>
     <t>General 1ra Base</t>
   </si>
   <si>
-    <t>0.74%</t>
+    <t>0.82%</t>
   </si>
   <si>
     <t>General 3ra Base</t>
   </si>
   <si>
-    <t>2.19%</t>
+    <t>3.02%</t>
   </si>
   <si>
     <t>Parrilladas</t>
@@ -124,13 +124,13 @@
     <t>Zona Gas Noel Butaca Central</t>
   </si>
   <si>
-    <t>44.18%</t>
+    <t>47.61%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>26.33%</t>
+    <t>27.12%</t>
   </si>
 </sst>
 </file>
@@ -643,7 +643,7 @@
         <v>828</v>
       </c>
       <c r="C6" s="6">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -667,7 +667,7 @@
         <v>22</v>
       </c>
       <c r="K6" s="6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>22</v>
@@ -676,16 +676,16 @@
         <v>22</v>
       </c>
       <c r="N6" s="6">
-        <v>43</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>22</v>
+        <v>69</v>
+      </c>
+      <c r="O6" s="6">
+        <v>2</v>
       </c>
       <c r="P6" s="6">
-        <v>340</v>
+        <v>381</v>
       </c>
       <c r="Q6" s="6">
-        <v>488</v>
+        <v>447</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -699,7 +699,7 @@
         <v>534</v>
       </c>
       <c r="C7" s="6">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -732,16 +732,16 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>157</v>
+        <v>107</v>
       </c>
       <c r="O7" s="6">
         <v>7</v>
       </c>
       <c r="P7" s="6">
-        <v>311</v>
+        <v>264</v>
       </c>
       <c r="Q7" s="6">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -767,7 +767,7 @@
         <v>22</v>
       </c>
       <c r="G8" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>22</v>
@@ -794,10 +794,10 @@
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q8" s="6">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -811,7 +811,7 @@
         <v>1324</v>
       </c>
       <c r="C9" s="6">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -850,10 +850,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="Q9" s="6">
-        <v>1295</v>
+        <v>1284</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -1035,13 +1035,13 @@
         <v>1109</v>
       </c>
       <c r="C13" s="6">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1068,16 +1068,16 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>40</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>22</v>
+        <v>43</v>
+      </c>
+      <c r="O13" s="6">
+        <v>3</v>
       </c>
       <c r="P13" s="6">
-        <v>490</v>
+        <v>528</v>
       </c>
       <c r="Q13" s="6">
-        <v>619</v>
+        <v>581</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>

--- a/data/asistencia/Bravos 2026.xlsx
+++ b/data/asistencia/Bravos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="40">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,25 +82,25 @@
     <t>-</t>
   </si>
   <si>
-    <t>46.01%</t>
+    <t>49.76%</t>
   </si>
   <si>
     <t>Butaca 3ra Base</t>
   </si>
   <si>
-    <t>49.44%</t>
+    <t>50.19%</t>
   </si>
   <si>
     <t>General 1ra Base</t>
   </si>
   <si>
-    <t>0.82%</t>
+    <t>0.91%</t>
   </si>
   <si>
     <t>General 3ra Base</t>
   </si>
   <si>
-    <t>3.02%</t>
+    <t>3.55%</t>
   </si>
   <si>
     <t>Parrilladas</t>
@@ -118,19 +118,19 @@
     <t>VIP</t>
   </si>
   <si>
-    <t>78.80%</t>
+    <t>81.52%</t>
   </si>
   <si>
     <t>Zona Gas Noel Butaca Central</t>
   </si>
   <si>
-    <t>47.61%</t>
+    <t>50.05%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>27.12%</t>
+    <t>28.55%</t>
   </si>
 </sst>
 </file>
@@ -643,7 +643,7 @@
         <v>828</v>
       </c>
       <c r="C6" s="6">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -667,7 +667,7 @@
         <v>22</v>
       </c>
       <c r="K6" s="6">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>22</v>
@@ -679,13 +679,13 @@
         <v>69</v>
       </c>
       <c r="O6" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P6" s="6">
-        <v>381</v>
+        <v>412</v>
       </c>
       <c r="Q6" s="6">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -699,7 +699,7 @@
         <v>534</v>
       </c>
       <c r="C7" s="6">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -738,10 +738,10 @@
         <v>7</v>
       </c>
       <c r="P7" s="6">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q7" s="6">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -755,7 +755,7 @@
         <v>1213</v>
       </c>
       <c r="C8" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -794,10 +794,10 @@
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q8" s="6">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -817,7 +817,7 @@
         <v>22</v>
       </c>
       <c r="E9" s="6">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
@@ -850,10 +850,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="Q9" s="6">
-        <v>1284</v>
+        <v>1277</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -985,7 +985,7 @@
         <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1012,16 +1012,16 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="Q12" s="6">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>35</v>
@@ -1035,7 +1035,7 @@
         <v>1109</v>
       </c>
       <c r="C13" s="6">
-        <v>283</v>
+        <v>312</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1053,7 +1053,7 @@
         <v>22</v>
       </c>
       <c r="I13" s="6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>22</v>
@@ -1070,14 +1070,14 @@
       <c r="N13" s="6">
         <v>43</v>
       </c>
-      <c r="O13" s="6">
-        <v>3</v>
+      <c r="O13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>528</v>
+        <v>555</v>
       </c>
       <c r="Q13" s="6">
-        <v>581</v>
+        <v>554</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>

--- a/data/asistencia/Bravos 2026.xlsx
+++ b/data/asistencia/Bravos 2026.xlsx
@@ -82,7 +82,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>49.76%</t>
+    <t>51.21%</t>
   </si>
   <si>
     <t>Butaca 3ra Base</t>
@@ -118,19 +118,19 @@
     <t>VIP</t>
   </si>
   <si>
-    <t>81.52%</t>
+    <t>82.88%</t>
   </si>
   <si>
     <t>Zona Gas Noel Butaca Central</t>
   </si>
   <si>
-    <t>50.05%</t>
+    <t>55.64%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>28.55%</t>
+    <t>29.97%</t>
   </si>
 </sst>
 </file>
@@ -643,7 +643,7 @@
         <v>828</v>
       </c>
       <c r="C6" s="6">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -678,14 +678,14 @@
       <c r="N6" s="6">
         <v>69</v>
       </c>
-      <c r="O6" s="6">
-        <v>4</v>
+      <c r="O6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="Q6" s="6">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -979,13 +979,13 @@
         <v>368</v>
       </c>
       <c r="C12" s="6">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1018,10 +1018,10 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q12" s="6">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>35</v>
@@ -1035,13 +1035,13 @@
         <v>1109</v>
       </c>
       <c r="C13" s="6">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1070,14 +1070,14 @@
       <c r="N13" s="6">
         <v>43</v>
       </c>
-      <c r="O13" s="6" t="s">
-        <v>22</v>
+      <c r="O13" s="6">
+        <v>4</v>
       </c>
       <c r="P13" s="6">
-        <v>555</v>
+        <v>617</v>
       </c>
       <c r="Q13" s="6">
-        <v>554</v>
+        <v>492</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>

--- a/data/asistencia/Bravos 2026.xlsx
+++ b/data/asistencia/Bravos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="40">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>51.21%</t>
+    <t>58.45%</t>
   </si>
   <si>
     <t>Butaca 3ra Base</t>
   </si>
   <si>
-    <t>50.19%</t>
+    <t>51.12%</t>
   </si>
   <si>
     <t>General 1ra Base</t>
@@ -100,13 +100,13 @@
     <t>General 3ra Base</t>
   </si>
   <si>
-    <t>3.55%</t>
+    <t>4.23%</t>
   </si>
   <si>
     <t>Parrilladas</t>
   </si>
   <si>
-    <t>0.00%</t>
+    <t>5.56%</t>
   </si>
   <si>
     <t>Personas con Discapacidad</t>
@@ -118,19 +118,19 @@
     <t>VIP</t>
   </si>
   <si>
-    <t>82.88%</t>
+    <t>87.23%</t>
   </si>
   <si>
     <t>Zona Gas Noel Butaca Central</t>
   </si>
   <si>
-    <t>55.64%</t>
+    <t>69.79%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>29.97%</t>
+    <t>34.57%</t>
   </si>
 </sst>
 </file>
@@ -643,7 +643,7 @@
         <v>828</v>
       </c>
       <c r="C6" s="6">
-        <v>252</v>
+        <v>314</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -676,16 +676,16 @@
         <v>22</v>
       </c>
       <c r="N6" s="6">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="Q6" s="6">
-        <v>404</v>
+        <v>344</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -699,7 +699,7 @@
         <v>534</v>
       </c>
       <c r="C7" s="6">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -734,14 +734,14 @@
       <c r="N7" s="6">
         <v>107</v>
       </c>
-      <c r="O7" s="6">
-        <v>7</v>
+      <c r="O7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="Q7" s="6">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -811,7 +811,7 @@
         <v>1324</v>
       </c>
       <c r="C9" s="6">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -850,10 +850,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="Q9" s="6">
-        <v>1277</v>
+        <v>1268</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -866,8 +866,8 @@
       <c r="B10" s="6">
         <v>180</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>22</v>
+      <c r="C10" s="6">
+        <v>10</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -905,11 +905,11 @@
       <c r="O10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P10" s="6" t="s">
-        <v>22</v>
+      <c r="P10" s="6">
+        <v>10</v>
       </c>
       <c r="Q10" s="6">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -979,13 +979,13 @@
         <v>368</v>
       </c>
       <c r="C12" s="6">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1012,16 +1012,16 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="Q12" s="6">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>35</v>
@@ -1035,13 +1035,13 @@
         <v>1109</v>
       </c>
       <c r="C13" s="6">
-        <v>329</v>
+        <v>451</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1071,13 +1071,13 @@
         <v>43</v>
       </c>
       <c r="O13" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P13" s="6">
-        <v>617</v>
+        <v>774</v>
       </c>
       <c r="Q13" s="6">
-        <v>492</v>
+        <v>335</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>

--- a/data/asistencia/Bravos 2026.xlsx
+++ b/data/asistencia/Bravos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="40">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,55 +82,55 @@
     <t>-</t>
   </si>
   <si>
-    <t>58.45%</t>
+    <t>100.00%</t>
   </si>
   <si>
     <t>Butaca 3ra Base</t>
   </si>
   <si>
-    <t>51.12%</t>
+    <t>98.69%</t>
   </si>
   <si>
     <t>General 1ra Base</t>
   </si>
   <si>
-    <t>0.91%</t>
+    <t>13.27%</t>
   </si>
   <si>
     <t>General 3ra Base</t>
   </si>
   <si>
-    <t>4.23%</t>
+    <t>31.80%</t>
   </si>
   <si>
     <t>Parrilladas</t>
   </si>
   <si>
-    <t>5.56%</t>
+    <t>11.11%</t>
   </si>
   <si>
     <t>Personas con Discapacidad</t>
   </si>
   <si>
-    <t>3.70%</t>
+    <t>59.26%</t>
   </si>
   <si>
     <t>VIP</t>
   </si>
   <si>
-    <t>87.23%</t>
+    <t>97.55%</t>
   </si>
   <si>
     <t>Zona Gas Noel Butaca Central</t>
   </si>
   <si>
-    <t>69.79%</t>
+    <t>99.82%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>34.57%</t>
+    <t>61.60%</t>
   </si>
 </sst>
 </file>
@@ -643,13 +643,13 @@
         <v>828</v>
       </c>
       <c r="C6" s="6">
-        <v>314</v>
+        <v>498</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="6">
-        <v>32</v>
+        <v>257</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
@@ -667,7 +667,7 @@
         <v>22</v>
       </c>
       <c r="K6" s="6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>22</v>
@@ -675,17 +675,17 @@
       <c r="M6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="6">
-        <v>67</v>
+      <c r="N6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>484</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>344</v>
+        <v>828</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -699,13 +699,13 @@
         <v>534</v>
       </c>
       <c r="C7" s="6">
-        <v>116</v>
+        <v>205</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>10</v>
+        <v>279</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -723,7 +723,7 @@
         <v>22</v>
       </c>
       <c r="K7" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>22</v>
@@ -732,16 +732,16 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>273</v>
+        <v>527</v>
       </c>
       <c r="Q7" s="6">
-        <v>261</v>
+        <v>7</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -755,13 +755,13 @@
         <v>1213</v>
       </c>
       <c r="C8" s="6">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>22</v>
+      <c r="E8" s="6">
+        <v>97</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -778,8 +778,8 @@
       <c r="J8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="6" t="s">
-        <v>22</v>
+      <c r="K8" s="6">
+        <v>4</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>22</v>
@@ -794,10 +794,10 @@
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>11</v>
+        <v>161</v>
       </c>
       <c r="Q8" s="6">
-        <v>1202</v>
+        <v>1052</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -811,13 +811,13 @@
         <v>1324</v>
       </c>
       <c r="C9" s="6">
-        <v>35</v>
+        <v>147</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="6">
-        <v>9</v>
+        <v>262</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
@@ -850,10 +850,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>56</v>
+        <v>421</v>
       </c>
       <c r="Q9" s="6">
-        <v>1268</v>
+        <v>903</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -867,7 +867,7 @@
         <v>180</v>
       </c>
       <c r="C10" s="6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -906,10 +906,10 @@
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Q10" s="6">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -922,14 +922,14 @@
       <c r="B11" s="6">
         <v>27</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>22</v>
+      <c r="C11" s="6">
+        <v>5</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>22</v>
+      <c r="E11" s="6">
+        <v>8</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -946,8 +946,8 @@
       <c r="J11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="6" t="s">
-        <v>22</v>
+      <c r="K11" s="6">
+        <v>2</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>22</v>
@@ -962,10 +962,10 @@
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Q11" s="6">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
@@ -979,13 +979,13 @@
         <v>368</v>
       </c>
       <c r="C12" s="6">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1012,16 +1012,16 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>321</v>
+        <v>359</v>
       </c>
       <c r="Q12" s="6">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>35</v>
@@ -1035,13 +1035,13 @@
         <v>1109</v>
       </c>
       <c r="C13" s="6">
-        <v>451</v>
+        <v>650</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>164</v>
+        <v>310</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1059,7 +1059,7 @@
         <v>22</v>
       </c>
       <c r="K13" s="6">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>22</v>
@@ -1068,16 +1068,16 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>43</v>
-      </c>
-      <c r="O13" s="6">
-        <v>6</v>
+        <v>34</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>774</v>
+        <v>1107</v>
       </c>
       <c r="Q13" s="6">
-        <v>335</v>
+        <v>2</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>
